--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -7175,7 +7175,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D201" t="n">
-        <v>6.604583581005206e-05</v>
+        <v>6.604583581005228e-05</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -13267,7 +13267,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D393" t="n">
-        <v>6.604583581005206e-05</v>
+        <v>6.604583581005228e-05</v>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -480,10 +480,10 @@
         <v>0.1555301732343423</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1577030284259995</v>
+        <v>0.1555301732343423</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.002172855191657164</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -516,10 +516,10 @@
         <v>0.2352362204724409</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2384525447696834</v>
+        <v>0.235236220472441</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.003216324297242473</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -552,10 +552,10 @@
         <v>0.1372549019607843</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1389295573894045</v>
+        <v>0.1372549019607843</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00167465542862022</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         <v>0.07363192750087139</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07542701920859002</v>
+        <v>0.07363192750087139</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001795091707718632</v>
+        <v>0</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>0.1123973114264376</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1135311603460642</v>
+        <v>0.1116504854368932</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.001133848919626548</v>
+        <v>0.0007468259895444251</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
         <v>0.1158402203856749</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1194260314603268</v>
+        <v>0.1158402203856749</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.003585811074651821</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>0.07547671251079663</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07751893506742004</v>
+        <v>0.0754767125107966</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00204222255662341</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -732,10 +732,10 @@
         <v>0.4321200621010868</v>
       </c>
       <c r="C9" t="n">
-        <v>0.432431799660819</v>
+        <v>0.4321200621010868</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0003117375597322392</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
         <v>0.04473180076628352</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0445243757431629</v>
+        <v>0.04300766283524904</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002074250231206276</v>
+        <v>0.001724137931034486</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         <v>0.1217257318952234</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1232877947141935</v>
+        <v>0.1217257318952234</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.001562062818970061</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         <v>0.1567337718424025</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1581512172482478</v>
+        <v>0.156600890306292</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.001417445405845263</v>
+        <v>0.0001328815361105462</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -876,10 +876,10 @@
         <v>0.09213863060016907</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09283898426847369</v>
+        <v>0.09206818822203439</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0007003536683046208</v>
+        <v>7.044237813468024e-05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>0.1298038977596989</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1302450561776762</v>
+        <v>0.1298038977596989</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0004411584179773165</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         <v>0.05766428954834752</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05821514337866949</v>
+        <v>0.05766428954834753</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0005508538303219679</v>
+        <v>-6.938893903907228e-18</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -984,10 +984,10 @@
         <v>0.01696020874103066</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0178028830579851</v>
+        <v>0.01686702078091511</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00084267431695444</v>
+        <v>9.318796011555108e-05</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>0.1153468385512584</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1161562995578362</v>
+        <v>0.1153468385512584</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0008094610065777635</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         <v>0.09707328872047086</v>
       </c>
       <c r="C18" t="n">
-        <v>0.09279946351390449</v>
+        <v>0.09126824155446264</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00427382520656637</v>
+        <v>0.005805047166008215</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
         <v>0.08442265795206971</v>
       </c>
       <c r="C19" t="n">
-        <v>0.08475262842693641</v>
+        <v>0.08431372549019608</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0003299704748667004</v>
+        <v>0.0001089324618736287</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1128,10 +1128,10 @@
         <v>0.2356821589205397</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2382142326312214</v>
+        <v>0.2356821589205398</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.00253207371068162</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         <v>0.4089955022488755</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4106628897860612</v>
+        <v>0.4089955022488755</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.001667387537185705</v>
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>0.09879032258064516</v>
       </c>
       <c r="C22" t="n">
-        <v>0.107177734375</v>
+        <v>0.09879032258064516</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.008387411794354843</v>
+        <v>0</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1236,10 +1236,10 @@
         <v>0.3233291822332918</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3242628667628668</v>
+        <v>0.3233291822332918</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0009336845295749852</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         <v>0.2549707602339181</v>
       </c>
       <c r="C24" t="n">
-        <v>0.255499970140066</v>
+        <v>0.2549707602339181</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0005292099061479094</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         <v>0.1552511415525114</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1578983415023069</v>
+        <v>0.1552511415525114</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.002647199949795537</v>
+        <v>0</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         <v>0.08646464646464647</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08778936507936508</v>
+        <v>0.08585858585858587</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.001324718614718612</v>
+        <v>0.0006060606060605961</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
         <v>0.0907563025210084</v>
       </c>
       <c r="C27" t="n">
-        <v>0.09412100711103358</v>
+        <v>0.09075630252100841</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.003364704590025178</v>
+        <v>-1.387778780781446e-17</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
         <v>0.2593758195646473</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2619009173873001</v>
+        <v>0.2593758195646472</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.002525097822652866</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D46" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D118" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D201" t="n">
-        <v>6.604583581005228e-05</v>
+        <v>6.604583581005206e-05</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -12007,7 +12007,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D352" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
@@ -13267,7 +13267,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D393" t="n">
-        <v>6.604583581005228e-05</v>
+        <v>6.604583581005206e-05</v>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
@@ -17411,7 +17411,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D541" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="inlineStr"/>
@@ -22728,10 +22728,10 @@
         <v>1.701669145658016e-05</v>
       </c>
       <c r="C731" t="n">
-        <v>9.570918650772567e-06</v>
+        <v>9.570108776918677e-06</v>
       </c>
       <c r="D731" t="n">
-        <v>7.445772805807592e-06</v>
+        <v>7.446582679661481e-06</v>
       </c>
       <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr"/>
@@ -22756,10 +22756,10 @@
         <v>1.314238148647551e-05</v>
       </c>
       <c r="C732" t="n">
-        <v>7.076834304401698e-06</v>
+        <v>7.076327637517688e-06</v>
       </c>
       <c r="D732" t="n">
-        <v>6.06554718207381e-06</v>
+        <v>6.066053848957821e-06</v>
       </c>
       <c r="E732" t="inlineStr"/>
       <c r="F732" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -1884,10 +1884,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C41" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D58" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D80" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4068,10 +4068,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C104" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D136" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6756,10 +6756,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D188" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D201" t="n">
-        <v>6.604583581005206e-05</v>
+        <v>6.604583581005228e-05</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -8388,10 +8388,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C239" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D239" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -10375,7 +10375,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D301" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -12804,10 +12804,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C377" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D377" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
@@ -13267,7 +13267,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D393" t="n">
-        <v>6.604583581005206e-05</v>
+        <v>6.604583581005228e-05</v>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
@@ -15000,10 +15000,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C455" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D455" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
@@ -19427,7 +19427,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D613" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr"/>
@@ -22644,10 +22644,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C728" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D728" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -1445,7 +1445,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1481,7 +1481,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1517,7 +1517,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1553,7 +1553,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1589,7 +1589,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1625,7 +1625,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1661,7 +1661,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1697,7 +1697,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1733,7 +1733,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1769,7 +1769,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1805,7 +1805,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1841,7 +1841,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1877,7 +1877,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1913,7 +1913,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1949,7 +1949,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1985,7 +1985,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2021,7 +2021,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2057,7 +2057,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2093,7 +2093,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2129,7 +2129,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2165,7 +2165,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2201,7 +2201,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2237,7 +2237,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2273,7 +2273,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2309,7 +2309,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2345,7 +2345,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2381,7 +2381,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2417,7 +2417,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2453,7 +2453,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2489,7 +2489,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2499,7 +2499,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D58" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2561,7 +2561,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2597,7 +2597,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2633,7 +2633,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2669,7 +2669,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2705,7 +2705,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2741,7 +2741,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2777,7 +2777,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2813,7 +2813,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2849,7 +2849,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2885,7 +2885,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2921,7 +2921,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2957,7 +2957,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2993,7 +2993,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -3029,7 +3029,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -3065,7 +3065,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -3101,7 +3101,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -3137,7 +3137,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3173,7 +3173,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -3209,7 +3209,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -3245,7 +3245,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -3281,17 +3281,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0.0008235294117647059</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -3353,7 +3353,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -3389,7 +3389,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3421,7 +3421,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3453,7 +3453,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3485,7 +3485,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3517,7 +3517,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3549,7 +3549,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3581,7 +3581,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3613,7 +3613,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3645,7 +3645,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -3677,7 +3677,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3709,7 +3709,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3741,7 +3741,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3773,7 +3773,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3805,7 +3805,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3837,7 +3837,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3869,7 +3869,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3901,7 +3901,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3933,7 +3933,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -3965,7 +3965,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -3997,7 +3997,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -4029,7 +4029,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -4061,7 +4061,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -4093,7 +4093,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -4125,7 +4125,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -4157,7 +4157,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -4189,7 +4189,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -4221,7 +4221,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -4253,7 +4253,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -4285,7 +4285,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -4317,7 +4317,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -4349,7 +4349,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -4381,7 +4381,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -4413,7 +4413,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4445,7 +4445,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -4477,7 +4477,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -4509,7 +4509,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -4541,7 +4541,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -4573,7 +4573,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -4605,7 +4605,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -4637,7 +4637,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -4669,7 +4669,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -4701,7 +4701,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -4733,7 +4733,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4765,7 +4765,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -4797,7 +4797,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4829,7 +4829,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -4861,7 +4861,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -4893,7 +4893,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -4925,7 +4925,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -4957,7 +4957,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -4989,7 +4989,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -5021,7 +5021,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -5053,7 +5053,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -5085,7 +5085,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -5095,7 +5095,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D136" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -5149,7 +5149,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -5181,7 +5181,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -5213,7 +5213,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -5245,7 +5245,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -5277,7 +5277,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -5309,7 +5309,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -5341,7 +5341,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -5373,7 +5373,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -5405,7 +5405,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -5437,7 +5437,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5469,7 +5469,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -5501,7 +5501,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5533,7 +5533,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5565,7 +5565,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -5597,7 +5597,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -5629,7 +5629,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -5661,7 +5661,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -5693,7 +5693,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -5725,7 +5725,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -5757,7 +5757,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -5789,7 +5789,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -5821,7 +5821,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -5853,7 +5853,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -5885,7 +5885,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -5917,7 +5917,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5949,7 +5949,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -5981,7 +5981,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -6013,7 +6013,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -6045,7 +6045,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -6077,7 +6077,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -6109,7 +6109,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -6141,7 +6141,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -6173,7 +6173,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -6205,7 +6205,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -6237,7 +6237,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -6269,7 +6269,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -6301,7 +6301,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -6333,7 +6333,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -6365,7 +6365,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -6397,7 +6397,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -6429,7 +6429,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -6461,7 +6461,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -6493,7 +6493,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -6525,7 +6525,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -6557,7 +6557,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -6589,7 +6589,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -6621,7 +6621,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -6653,7 +6653,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -6685,7 +6685,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -6717,7 +6717,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -6749,17 +6749,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>0.0008235294117647059</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -6813,7 +6813,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -6845,7 +6845,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -6877,7 +6877,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -6909,7 +6909,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6941,7 +6941,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -6973,7 +6973,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -7005,7 +7005,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -7037,7 +7037,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -7069,7 +7069,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -7101,7 +7101,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -7133,7 +7133,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -7165,7 +7165,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -7197,7 +7197,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -7229,7 +7229,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -7261,7 +7261,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -7293,7 +7293,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -7325,7 +7325,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -7357,7 +7357,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -7389,7 +7389,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -7421,7 +7421,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -7453,7 +7453,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -7485,7 +7485,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -7517,7 +7517,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -7549,7 +7549,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -7581,7 +7581,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -7613,7 +7613,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -7645,7 +7645,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -7677,7 +7677,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -7709,7 +7709,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -7741,7 +7741,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -7773,7 +7773,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -7805,7 +7805,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -7837,7 +7837,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -7869,7 +7869,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -7901,7 +7901,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -7933,7 +7933,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -7965,7 +7965,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -7997,7 +7997,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -8029,7 +8029,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -8061,7 +8061,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -8093,7 +8093,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -8125,7 +8125,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -8157,7 +8157,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -8189,7 +8189,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -8221,7 +8221,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -8253,7 +8253,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -8285,7 +8285,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -8317,7 +8317,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -8349,7 +8349,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -8381,7 +8381,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -8413,7 +8413,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -8445,7 +8445,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -8477,7 +8477,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -8509,7 +8509,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -8541,7 +8541,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -8573,7 +8573,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -8605,7 +8605,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -8637,7 +8637,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -8669,7 +8669,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -8701,7 +8701,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -8733,7 +8733,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -8765,7 +8765,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -8797,7 +8797,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -8829,7 +8829,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -8861,7 +8861,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -8893,7 +8893,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -8925,7 +8925,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -8957,7 +8957,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -8989,7 +8989,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -9021,7 +9021,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -9053,7 +9053,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -9085,7 +9085,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -9117,7 +9117,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -9149,7 +9149,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -9181,7 +9181,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -9213,7 +9213,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -9245,7 +9245,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -9277,7 +9277,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -9309,7 +9309,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -9341,7 +9341,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -9373,7 +9373,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -9405,7 +9405,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -9437,7 +9437,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -9469,7 +9469,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -9501,7 +9501,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -9533,7 +9533,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -9565,7 +9565,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -9597,7 +9597,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -9629,7 +9629,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -9661,7 +9661,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -9693,7 +9693,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -9725,7 +9725,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -9757,7 +9757,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -9789,7 +9789,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -9821,7 +9821,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -9853,7 +9853,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -9885,7 +9885,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -9917,7 +9917,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -9949,7 +9949,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -9981,7 +9981,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -10013,7 +10013,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -10045,7 +10045,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -10077,7 +10077,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -10109,7 +10109,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -10141,7 +10141,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -10173,7 +10173,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -10205,7 +10205,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -10237,7 +10237,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -10269,7 +10269,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -10301,7 +10301,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -10333,7 +10333,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -10365,7 +10365,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -10375,7 +10375,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D301" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -10397,7 +10397,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -10429,7 +10429,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -10461,7 +10461,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -10493,7 +10493,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -10525,7 +10525,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -10557,7 +10557,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -10589,7 +10589,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -10621,7 +10621,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -10653,7 +10653,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -10685,7 +10685,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -10717,7 +10717,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -10749,7 +10749,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -10781,7 +10781,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -10813,7 +10813,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -10845,7 +10845,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -10877,7 +10877,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -10909,7 +10909,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -10941,7 +10941,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -10973,7 +10973,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -11005,7 +11005,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -11037,7 +11037,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -11069,7 +11069,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -11101,7 +11101,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -11133,7 +11133,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -11165,7 +11165,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -11197,7 +11197,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -11229,7 +11229,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -11261,7 +11261,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -11293,7 +11293,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -11325,7 +11325,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -11357,7 +11357,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -11389,7 +11389,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -11421,7 +11421,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -11453,7 +11453,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -11485,7 +11485,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -11517,7 +11517,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -11549,7 +11549,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -11581,7 +11581,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -11613,7 +11613,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -11645,7 +11645,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -11677,7 +11677,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -11709,7 +11709,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -11741,7 +11741,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -11773,7 +11773,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -11805,7 +11805,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -11837,7 +11837,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -11869,7 +11869,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -11901,7 +11901,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -11933,7 +11933,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -11965,7 +11965,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -11997,7 +11997,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -12029,7 +12029,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -12061,7 +12061,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -12093,7 +12093,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -12125,7 +12125,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -12157,7 +12157,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -12189,7 +12189,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -12221,7 +12221,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -12253,7 +12253,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -12285,7 +12285,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -12317,7 +12317,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -12349,7 +12349,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -12381,7 +12381,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -12413,7 +12413,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -12445,7 +12445,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -12477,7 +12477,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -12509,7 +12509,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -12541,7 +12541,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -12573,7 +12573,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -12605,7 +12605,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -12637,7 +12637,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -12669,7 +12669,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -12701,7 +12701,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -12733,7 +12733,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -12765,7 +12765,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -12797,17 +12797,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B377" t="n">
         <v>0.0008235294117647059</v>
       </c>
       <c r="C377" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D377" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
@@ -12829,7 +12829,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -12861,7 +12861,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -12893,7 +12893,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -12921,7 +12921,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -12949,7 +12949,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -12977,7 +12977,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -13005,7 +13005,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -13033,7 +13033,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -13061,7 +13061,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -13089,7 +13089,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -13117,7 +13117,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -13145,7 +13145,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -13173,7 +13173,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -13201,7 +13201,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -13229,7 +13229,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -13257,7 +13257,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -13285,7 +13285,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -13313,7 +13313,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -13341,7 +13341,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -13369,7 +13369,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -13397,7 +13397,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -13425,7 +13425,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -13453,7 +13453,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -13481,7 +13481,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -13509,7 +13509,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -13537,7 +13537,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -13565,7 +13565,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -13593,7 +13593,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -13621,7 +13621,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -13649,7 +13649,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -13677,7 +13677,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -13705,7 +13705,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -13733,7 +13733,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -13761,7 +13761,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -13789,7 +13789,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -13817,7 +13817,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -13845,7 +13845,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -13873,7 +13873,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -13901,7 +13901,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -13929,7 +13929,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -13957,7 +13957,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -13985,7 +13985,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -14013,7 +14013,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -14041,7 +14041,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -14069,7 +14069,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -14097,7 +14097,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -14125,7 +14125,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -14153,7 +14153,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -14181,7 +14181,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -14209,7 +14209,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -14237,7 +14237,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -14265,7 +14265,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -14293,7 +14293,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -14321,7 +14321,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -14349,7 +14349,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -14377,7 +14377,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -14405,7 +14405,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -14433,7 +14433,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -14461,7 +14461,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -14489,7 +14489,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -14517,7 +14517,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -14545,7 +14545,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -14573,7 +14573,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -14601,7 +14601,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -14629,7 +14629,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -14657,7 +14657,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -14685,7 +14685,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -14713,7 +14713,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -14741,7 +14741,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -14769,7 +14769,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -14797,7 +14797,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -14825,7 +14825,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -14853,7 +14853,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -14881,7 +14881,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -14909,7 +14909,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -14937,7 +14937,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -14965,7 +14965,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -14993,7 +14993,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -15021,7 +15021,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -15049,7 +15049,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -15077,7 +15077,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -15105,7 +15105,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -15133,7 +15133,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -15161,7 +15161,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -15189,7 +15189,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -15217,7 +15217,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -15245,7 +15245,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -15273,7 +15273,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -15301,7 +15301,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -15329,7 +15329,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -15357,7 +15357,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -15385,7 +15385,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -15413,7 +15413,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -15441,7 +15441,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -15469,7 +15469,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -15497,7 +15497,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -15525,7 +15525,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -15553,7 +15553,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -15581,7 +15581,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -15609,7 +15609,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -15637,7 +15637,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -15665,7 +15665,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -15693,7 +15693,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -15721,7 +15721,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -15749,7 +15749,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -15777,7 +15777,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -15805,7 +15805,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -15833,7 +15833,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -15861,7 +15861,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -15889,7 +15889,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -15917,7 +15917,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -15945,7 +15945,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -15973,7 +15973,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -16001,7 +16001,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -16029,7 +16029,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -16057,7 +16057,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -16085,7 +16085,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -16113,7 +16113,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -16141,7 +16141,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -16169,7 +16169,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -16197,7 +16197,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -16225,7 +16225,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -16253,7 +16253,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -16281,7 +16281,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -16309,7 +16309,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -16337,7 +16337,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -16365,7 +16365,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -16393,7 +16393,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -16421,7 +16421,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -16449,7 +16449,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -16477,7 +16477,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -16505,7 +16505,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -16533,7 +16533,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -16561,7 +16561,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -16589,7 +16589,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -16617,7 +16617,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -16645,7 +16645,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -16673,7 +16673,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -16701,7 +16701,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -16729,7 +16729,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -16757,7 +16757,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -16785,7 +16785,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -16813,7 +16813,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -16841,7 +16841,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -16869,7 +16869,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -16897,7 +16897,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -16925,7 +16925,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -16953,7 +16953,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -16981,7 +16981,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -17009,7 +17009,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -17037,7 +17037,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -17065,7 +17065,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -17093,7 +17093,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -17121,7 +17121,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -17149,7 +17149,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -17177,7 +17177,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -17205,7 +17205,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -17233,7 +17233,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -17261,7 +17261,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -17289,7 +17289,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -17317,7 +17317,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -17345,7 +17345,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -17373,7 +17373,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -17401,7 +17401,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -17429,7 +17429,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -17457,7 +17457,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -17485,7 +17485,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -17513,7 +17513,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -17541,7 +17541,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -17569,7 +17569,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -17597,7 +17597,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -17625,7 +17625,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -17653,7 +17653,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -17681,7 +17681,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -17709,7 +17709,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -17737,7 +17737,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -17765,7 +17765,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -17793,7 +17793,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -17821,7 +17821,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -17849,7 +17849,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B557" t="n">
@@ -17877,7 +17877,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B558" t="n">
@@ -17905,7 +17905,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B559" t="n">
@@ -17933,7 +17933,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B560" t="n">
@@ -17961,7 +17961,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B561" t="n">
@@ -17989,7 +17989,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B562" t="n">
@@ -18017,7 +18017,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B563" t="n">
@@ -18045,7 +18045,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B564" t="n">
@@ -18073,7 +18073,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B565" t="n">
@@ -18101,7 +18101,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B566" t="n">
@@ -18129,7 +18129,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B567" t="n">
@@ -18157,7 +18157,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B568" t="n">
@@ -18185,7 +18185,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B569" t="n">
@@ -18213,7 +18213,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B570" t="n">
@@ -18241,7 +18241,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B571" t="n">
@@ -18269,7 +18269,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B572" t="n">
@@ -18297,7 +18297,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B573" t="n">
@@ -18325,7 +18325,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B574" t="n">
@@ -18353,7 +18353,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B575" t="n">
@@ -18381,7 +18381,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B576" t="n">
@@ -18409,7 +18409,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B577" t="n">
@@ -18437,7 +18437,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B578" t="n">
@@ -18465,7 +18465,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B579" t="n">
@@ -18493,7 +18493,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B580" t="n">
@@ -18521,7 +18521,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B581" t="n">
@@ -18549,7 +18549,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B582" t="n">
@@ -18577,7 +18577,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B583" t="n">
@@ -18605,7 +18605,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B584" t="n">
@@ -18633,7 +18633,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B585" t="n">
@@ -18661,7 +18661,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B586" t="n">
@@ -18689,7 +18689,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B587" t="n">
@@ -18717,7 +18717,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B588" t="n">
@@ -18745,7 +18745,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B589" t="n">
@@ -18773,7 +18773,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B590" t="n">
@@ -18801,7 +18801,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B591" t="n">
@@ -18829,7 +18829,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B592" t="n">
@@ -18857,7 +18857,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B593" t="n">
@@ -18885,7 +18885,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B594" t="n">
@@ -18913,7 +18913,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B595" t="n">
@@ -18941,7 +18941,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B596" t="n">
@@ -18969,7 +18969,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B597" t="n">
@@ -18997,7 +18997,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B598" t="n">
@@ -19025,7 +19025,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B599" t="n">
@@ -19053,7 +19053,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B600" t="n">
@@ -19081,7 +19081,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B601" t="n">
@@ -19109,7 +19109,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B602" t="n">
@@ -19137,7 +19137,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B603" t="n">
@@ -19165,7 +19165,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B604" t="n">
@@ -19193,7 +19193,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -19221,7 +19221,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B606" t="n">
@@ -19249,7 +19249,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B607" t="n">
@@ -19277,7 +19277,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B608" t="n">
@@ -19305,7 +19305,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B609" t="n">
@@ -19333,7 +19333,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B610" t="n">
@@ -19361,7 +19361,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B611" t="n">
@@ -19389,7 +19389,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B612" t="n">
@@ -19417,7 +19417,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B613" t="n">
@@ -19427,7 +19427,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D613" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr"/>
@@ -19445,7 +19445,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B614" t="n">
@@ -19473,7 +19473,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B615" t="n">
@@ -19501,7 +19501,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B616" t="n">
@@ -19529,7 +19529,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B617" t="n">
@@ -19557,7 +19557,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B618" t="n">
@@ -19585,7 +19585,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B619" t="n">
@@ -19613,7 +19613,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B620" t="n">
@@ -19641,7 +19641,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B621" t="n">
@@ -19669,7 +19669,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B622" t="n">
@@ -19697,7 +19697,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B623" t="n">
@@ -19725,7 +19725,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B624" t="n">
@@ -19753,7 +19753,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B625" t="n">
@@ -19781,7 +19781,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B626" t="n">
@@ -19809,7 +19809,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B627" t="n">
@@ -19837,7 +19837,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B628" t="n">
@@ -19865,7 +19865,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B629" t="n">
@@ -19893,7 +19893,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B630" t="n">
@@ -19921,7 +19921,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B631" t="n">
@@ -19949,7 +19949,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B632" t="n">
@@ -19977,7 +19977,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B633" t="n">
@@ -20005,7 +20005,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B634" t="n">
@@ -20033,7 +20033,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -20061,7 +20061,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B636" t="n">
@@ -20089,7 +20089,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B637" t="n">
@@ -20117,7 +20117,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B638" t="n">
@@ -20145,7 +20145,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B639" t="n">
@@ -20173,7 +20173,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B640" t="n">
@@ -20201,7 +20201,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B641" t="n">
@@ -20229,7 +20229,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B642" t="n">
@@ -20257,7 +20257,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B643" t="n">
@@ -20285,7 +20285,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B644" t="n">
@@ -20313,7 +20313,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B645" t="n">
@@ -20341,7 +20341,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B646" t="n">
@@ -20369,7 +20369,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B647" t="n">
@@ -20397,7 +20397,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B648" t="n">
@@ -20425,7 +20425,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B649" t="n">
@@ -20453,7 +20453,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B650" t="n">
@@ -20481,7 +20481,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -20509,7 +20509,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -20537,7 +20537,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B653" t="n">
@@ -20565,7 +20565,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B654" t="n">
@@ -20593,7 +20593,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B655" t="n">
@@ -20621,7 +20621,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B656" t="n">
@@ -20649,7 +20649,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B657" t="n">
@@ -20677,7 +20677,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B658" t="n">
@@ -20705,7 +20705,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B659" t="n">
@@ -20733,7 +20733,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B660" t="n">
@@ -20761,7 +20761,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B661" t="n">
@@ -20789,7 +20789,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B662" t="n">
@@ -20817,7 +20817,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B663" t="n">
@@ -20845,7 +20845,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B664" t="n">
@@ -20873,7 +20873,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B665" t="n">
@@ -20901,7 +20901,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B666" t="n">
@@ -20929,7 +20929,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B667" t="n">
@@ -20957,7 +20957,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B668" t="n">
@@ -20985,7 +20985,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B669" t="n">
@@ -21013,7 +21013,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B670" t="n">
@@ -21041,7 +21041,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -21069,7 +21069,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B672" t="n">
@@ -21097,7 +21097,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B673" t="n">
@@ -21125,7 +21125,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B674" t="n">
@@ -21153,7 +21153,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B675" t="n">
@@ -21181,7 +21181,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B676" t="n">
@@ -21209,7 +21209,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B677" t="n">
@@ -21237,7 +21237,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B678" t="n">
@@ -21265,7 +21265,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B679" t="n">
@@ -21293,7 +21293,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B680" t="n">
@@ -21321,7 +21321,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B681" t="n">
@@ -21349,7 +21349,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B682" t="n">
@@ -21377,7 +21377,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B683" t="n">
@@ -21405,7 +21405,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B684" t="n">
@@ -21433,7 +21433,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B685" t="n">
@@ -21461,7 +21461,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B686" t="n">
@@ -21489,7 +21489,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B687" t="n">
@@ -21517,7 +21517,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B688" t="n">
@@ -21545,7 +21545,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B689" t="n">
@@ -21573,7 +21573,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B690" t="n">
@@ -21601,7 +21601,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B691" t="n">
@@ -21629,7 +21629,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B692" t="n">
@@ -21657,7 +21657,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B693" t="n">
@@ -21685,7 +21685,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B694" t="n">
@@ -21713,7 +21713,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B695" t="n">
@@ -21741,7 +21741,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B696" t="n">
@@ -21769,7 +21769,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B697" t="n">
@@ -21797,7 +21797,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B698" t="n">
@@ -21825,7 +21825,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B699" t="n">
@@ -21853,7 +21853,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B700" t="n">
@@ -21881,7 +21881,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B701" t="n">
@@ -21909,7 +21909,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B702" t="n">
@@ -21937,7 +21937,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B703" t="n">
@@ -21965,7 +21965,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B704" t="n">
@@ -21993,7 +21993,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B705" t="n">
@@ -22021,7 +22021,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B706" t="n">
@@ -22049,7 +22049,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B707" t="n">
@@ -22077,7 +22077,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B708" t="n">
@@ -22105,7 +22105,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B709" t="n">
@@ -22133,7 +22133,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B710" t="n">
@@ -22161,7 +22161,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B711" t="n">
@@ -22189,7 +22189,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B712" t="n">
@@ -22217,7 +22217,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B713" t="n">
@@ -22245,7 +22245,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B714" t="n">
@@ -22273,7 +22273,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B715" t="n">
@@ -22301,7 +22301,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B716" t="n">
@@ -22329,7 +22329,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B717" t="n">
@@ -22357,7 +22357,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B718" t="n">
@@ -22385,7 +22385,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B719" t="n">
@@ -22413,7 +22413,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B720" t="n">
@@ -22441,7 +22441,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B721" t="n">
@@ -22469,7 +22469,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B722" t="n">
@@ -22497,7 +22497,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B723" t="n">
@@ -22525,7 +22525,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B724" t="n">
@@ -22553,7 +22553,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B725" t="n">
@@ -22581,7 +22581,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B726" t="n">
@@ -22609,7 +22609,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B727" t="n">
@@ -22637,17 +22637,17 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B728" t="n">
         <v>0.0008235294117647059</v>
       </c>
       <c r="C728" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D728" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr"/>
@@ -22665,7 +22665,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B729" t="n">
@@ -22693,7 +22693,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B730" t="n">

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -22721,7 +22721,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Pre-immune repertoire</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B731" t="n">
@@ -22749,7 +22749,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Pre-immune repertoire</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B732" t="n">

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -1884,10 +1884,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C41" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4068,10 +4068,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C104" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D201" t="n">
-        <v>6.604583581005228e-05</v>
+        <v>6.604583581005206e-05</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -8388,10 +8388,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C239" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D239" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -12007,7 +12007,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D352" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
@@ -13267,7 +13267,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D393" t="n">
-        <v>6.604583581005228e-05</v>
+        <v>6.604583581005206e-05</v>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
@@ -15000,10 +15000,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C455" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D455" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
@@ -17411,7 +17411,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D541" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -2499,7 +2499,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D58" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D136" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6756,10 +6756,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D201" t="n">
-        <v>6.604583581005228e-05</v>
+        <v>6.604583581005206e-05</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -10375,7 +10375,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D301" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -12804,10 +12804,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C377" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D377" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
@@ -13267,7 +13267,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D393" t="n">
-        <v>6.604583581005228e-05</v>
+        <v>6.604583581005206e-05</v>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
@@ -19427,7 +19427,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D613" t="n">
-        <v>4.025278750553404e-05</v>
+        <v>4.025278750553578e-05</v>
       </c>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr"/>
@@ -22644,10 +22644,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C728" t="n">
-        <v>0.0008235294117647059</v>
+        <v>0.0008235294117647058</v>
       </c>
       <c r="D728" t="n">
-        <v>0</v>
+        <v>1.084202172485504e-19</v>
       </c>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -1884,10 +1884,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C41" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D46" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4068,10 +4068,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C104" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D118" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -8388,10 +8388,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C239" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D239" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -12007,7 +12007,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D352" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
@@ -15000,10 +15000,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C455" t="n">
-        <v>0.004554655870445345</v>
+        <v>0.004554655870445344</v>
       </c>
       <c r="D455" t="n">
-        <v>0.0005060728744939267</v>
+        <v>0.0005060728744939276</v>
       </c>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
@@ -17411,7 +17411,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D541" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0</v>
       </c>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_vgene_decomposition_CDR3b.xlsx
@@ -1884,10 +1884,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C41" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D58" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D80" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4068,10 +4068,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C104" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D136" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -6756,10 +6756,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D188" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D201" t="n">
-        <v>6.604583581005206e-05</v>
+        <v>6.604583581005228e-05</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
@@ -8388,10 +8388,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C239" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D239" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
@@ -10375,7 +10375,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D301" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
@@ -12007,7 +12007,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D352" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
@@ -12804,10 +12804,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C377" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D377" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
@@ -13267,7 +13267,7 @@
         <v>0.001386962552011096</v>
       </c>
       <c r="D393" t="n">
-        <v>6.604583581005206e-05</v>
+        <v>6.604583581005228e-05</v>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
@@ -15000,10 +15000,10 @@
         <v>0.005060728744939271</v>
       </c>
       <c r="C455" t="n">
-        <v>0.004554655870445344</v>
+        <v>0.004554655870445345</v>
       </c>
       <c r="D455" t="n">
-        <v>0.0005060728744939276</v>
+        <v>0.0005060728744939267</v>
       </c>
       <c r="E455" t="inlineStr"/>
       <c r="F455" t="inlineStr"/>
@@ -17411,7 +17411,7 @@
         <v>0.0172229393324728</v>
       </c>
       <c r="D541" t="n">
-        <v>0</v>
+        <v>3.469446951953614e-18</v>
       </c>
       <c r="E541" t="inlineStr"/>
       <c r="F541" t="inlineStr"/>
@@ -19427,7 +19427,7 @@
         <v>0.01296139757678219</v>
       </c>
       <c r="D613" t="n">
-        <v>4.025278750553578e-05</v>
+        <v>4.025278750553404e-05</v>
       </c>
       <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr"/>
@@ -22644,10 +22644,10 @@
         <v>0.0008235294117647059</v>
       </c>
       <c r="C728" t="n">
-        <v>0.0008235294117647058</v>
+        <v>0.0008235294117647059</v>
       </c>
       <c r="D728" t="n">
-        <v>1.084202172485504e-19</v>
+        <v>0</v>
       </c>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr"/>
